--- a/outputs/HMT-CAT-EYE-001/bigseller_product_upload.xlsx
+++ b/outputs/HMT-CAT-EYE-001/bigseller_product_upload.xlsx
@@ -622,7 +622,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>100350</t>
+          <t>102029</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>100350</t>
+          <t>102029</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -860,7 +860,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>100350</t>
+          <t>102029</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -979,7 +979,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>100350</t>
+          <t>102029</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
